--- a/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
+++ b/qtp_pyaez/data_input/crop_inputs/input_crop_tsum_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/crop_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9138EF93-EDEC-2F44-A7CE-D3A6C7C8C5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E47AA1-EDD9-ED49-BC45-27F5FCDE72E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="10000" windowHeight="17980" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="26020" windowHeight="16340" xr2:uid="{6A344343-B7DE-634F-8641-8E08B91FD93F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
